--- a/data/CPR_coordinates.xlsx
+++ b/data/CPR_coordinates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nocacuk-my.sharepoint.com/personal/nathu_noc_ac_uk/Documents/Documents/AtlantECO/JC237/CPR/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nathu\Documents\github\RoCSI-CPR_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="14_{50168930-9B3A-456A-8018-17BEC0EC1EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A444EC10-6479-4B2D-B3BE-CF9A4D7E2B49}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A25176C-503C-4E8F-ADE8-772D942382DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C4A74FAD-FC2F-4434-A932-692CFDA4D976}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{C4A74FAD-FC2F-4434-A932-692CFDA4D976}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -680,9 +680,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{930FE7FA-C65D-4FF4-9DF4-D3E531B00930}">
   <dimension ref="A1:D86"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>86</v>
       </c>
@@ -696,7 +696,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -710,7 +710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -718,13 +718,13 @@
         <v>50.491</v>
       </c>
       <c r="C3" s="3">
-        <v>-1.8268333333333333</v>
+        <v>-1.426833</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -738,7 +738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -752,7 +752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -766,7 +766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
@@ -780,7 +780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
@@ -794,7 +794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
@@ -808,7 +808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -822,7 +822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -836,7 +836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -850,7 +850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
@@ -864,7 +864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -878,7 +878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
@@ -892,7 +892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
@@ -906,7 +906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -920,7 +920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -934,7 +934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -948,7 +948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -962,7 +962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>20</v>
       </c>
@@ -976,7 +976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>21</v>
       </c>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>22</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>27</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>28</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>29</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>31</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>32</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>35</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>36</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>37</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>40</v>
       </c>
@@ -1256,7 +1256,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
@@ -1270,7 +1270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>42</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>44</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>45</v>
       </c>
@@ -1326,7 +1326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>46</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>47</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>48</v>
       </c>
@@ -1368,7 +1368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>49</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>50</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>51</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
@@ -1424,7 +1424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>53</v>
       </c>
@@ -1432,13 +1432,13 @@
         <v>48.663566000000003</v>
       </c>
       <c r="C54" s="7">
-        <v>-15.080075166666667</v>
+        <v>-15.800751666667001</v>
       </c>
       <c r="D54">
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>54</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>55</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>56</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>57</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>58</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>59</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>60</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>61</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>62</v>
       </c>
@@ -1564,12 +1564,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B64" s="6">
-        <v>48.62923</v>
+        <v>48.503383999999997</v>
       </c>
       <c r="C64" s="7">
         <v>-12.581061999999999</v>
@@ -1578,7 +1578,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>65</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>66</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>67</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>68</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>69</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>70</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>71</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>72</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>73</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>74</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>75</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>76</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>77</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>78</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>79</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>80</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>81</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>82</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>83</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>84</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>85</v>
       </c>
@@ -1892,11 +1892,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="2d1e7cac-54ad-4188-bc3e-0629298f93aa" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2139,27 +2140,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="2d1e7cac-54ad-4188-bc3e-0629298f93aa" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB912A2C-0722-4B07-84AD-9DFEEFD28AA6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09ABCEC1-6789-4021-9D09-B198175D3E49}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="b793d5a7-62fa-46a1-a57c-8fd18839ff7c"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2d1e7cac-54ad-4188-bc3e-0629298f93aa"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2184,9 +2175,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{09ABCEC1-6789-4021-9D09-B198175D3E49}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB912A2C-0722-4B07-84AD-9DFEEFD28AA6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="b793d5a7-62fa-46a1-a57c-8fd18839ff7c"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2d1e7cac-54ad-4188-bc3e-0629298f93aa"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>